--- a/fhir/StructureDefinition-ehealth-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -656,7 +656,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -702,7 +702,7 @@
   </si>
   <si>
     <t>Attachment
-Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
+Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
   </si>
   <si>
     <t>Source from which this consent is taken</t>
@@ -838,7 +838,7 @@
     <t>Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -875,7 +875,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -973,13 +973,13 @@
     <t>How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1010,7 +1010,7 @@
     <t>Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -1032,7 +1032,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.purpose</t>
@@ -1134,7 +1134,7 @@
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>

--- a/fhir/StructureDefinition-ehealth-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-consent.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="369">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -718,6 +718,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Field 19 Informational Material Supplied Indicator</t>
   </si>
   <si>
@@ -728,6 +731,16 @@
   </si>
   <si>
     <t xml:space="preserve">Reference(http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-consent|http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-documentreference|Contract|http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-questionnaireresponse)
+</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment</t>
+  </si>
+  <si>
+    <t>sourceAttachment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attachment
 </t>
   </si>
   <si>
@@ -1448,12 +1461,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN60"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.33203125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.33203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="15.390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3736,7 +3749,7 @@
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>218</v>
@@ -3757,7 +3770,7 @@
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>75</v>
@@ -3768,13 +3781,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>218</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>75</v>
@@ -3796,7 +3809,7 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>220</v>
@@ -3873,7 +3886,7 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>75</v>
@@ -3884,12 +3897,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>75</v>
       </c>
@@ -3898,7 +3913,7 @@
         <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>75</v>
@@ -3907,18 +3922,20 @@
         <v>75</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>75</v>
@@ -3967,13 +3984,13 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>75</v>
@@ -3985,7 +4002,7 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>75</v>
@@ -4010,7 +4027,7 @@
         <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>75</v>
@@ -4079,19 +4096,19 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -4100,7 +4117,7 @@
         <v>75</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>75</v>
@@ -4108,21 +4125,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>75</v>
@@ -4134,17 +4151,15 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>75</v>
@@ -4193,28 +4208,28 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>75</v>
@@ -4229,7 +4244,7 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>243</v>
+        <v>146</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4242,26 +4257,24 @@
         <v>75</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O25" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4309,7 +4322,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4330,7 +4343,7 @@
         <v>75</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>130</v>
+        <v>241</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>75</v>
@@ -4338,33 +4351,33 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>248</v>
@@ -4372,8 +4385,12 @@
       <c r="M26" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="N26" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4421,19 +4438,19 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
@@ -4442,7 +4459,7 @@
         <v>75</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>75</v>
@@ -4482,11 +4499,9 @@
         <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N27" t="s" s="2">
         <v>253</v>
       </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4511,11 +4526,13 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>254</v>
+        <v>75</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -4542,7 +4559,7 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>99</v>
@@ -4585,23 +4602,21 @@
         <v>75</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>174</v>
+        <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>256</v>
       </c>
       <c r="M28" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>259</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4625,13 +4640,11 @@
         <v>75</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>75</v>
@@ -4658,7 +4671,7 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>99</v>
@@ -4678,10 +4691,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4692,7 +4705,7 @@
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>75</v>
@@ -4704,16 +4717,20 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>229</v>
+        <v>174</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
@@ -4737,13 +4754,13 @@
         <v>75</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>75</v>
+        <v>265</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>75</v>
@@ -4761,16 +4778,16 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -4790,10 +4807,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4804,7 +4821,7 @@
         <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>75</v>
@@ -4813,16 +4830,16 @@
         <v>75</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>233</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4873,19 +4890,19 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
@@ -4894,7 +4911,7 @@
         <v>75</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>75</v>
@@ -4902,21 +4919,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>75</v>
@@ -4928,17 +4945,15 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M31" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -4987,28 +5002,28 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>75</v>
@@ -5016,14 +5031,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>243</v>
+        <v>146</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5036,26 +5051,24 @@
         <v>75</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O32" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>75</v>
       </c>
@@ -5103,7 +5116,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5124,7 +5137,7 @@
         <v>75</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>130</v>
+        <v>241</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>75</v>
@@ -5132,42 +5145,46 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>270</v>
+        <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
       </c>
@@ -5215,19 +5232,19 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -5236,7 +5253,7 @@
         <v>75</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>75</v>
@@ -5255,7 +5272,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>87</v>
@@ -5267,7 +5284,7 @@
         <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>274</v>
@@ -5330,7 +5347,7 @@
         <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>87</v>
@@ -5382,13 +5399,13 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>195</v>
+        <v>278</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5468,10 +5485,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5491,16 +5508,16 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5551,7 +5568,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5580,10 +5597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5603,16 +5620,16 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>233</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>234</v>
+        <v>285</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>235</v>
+        <v>286</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5663,7 +5680,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5675,7 +5692,7 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
@@ -5684,7 +5701,7 @@
         <v>75</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>75</v>
@@ -5692,21 +5709,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -5718,17 +5735,15 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -5777,28 +5792,28 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
@@ -5806,14 +5821,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>243</v>
+        <v>146</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5826,26 +5841,24 @@
         <v>75</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O39" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
       </c>
@@ -5893,7 +5906,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5914,7 +5927,7 @@
         <v>75</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>130</v>
+        <v>241</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -5922,42 +5935,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -5981,13 +5998,13 @@
         <v>75</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>290</v>
+        <v>75</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>75</v>
@@ -6005,19 +6022,19 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>75</v>
@@ -6026,7 +6043,7 @@
         <v>75</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>75</v>
@@ -6034,10 +6051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6060,13 +6077,13 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6093,13 +6110,13 @@
         <v>75</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>75</v>
+        <v>293</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>75</v>
+        <v>294</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>75</v>
@@ -6117,7 +6134,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6160,7 +6177,7 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -6169,25 +6186,23 @@
         <v>75</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>229</v>
+        <v>296</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q42" t="s" s="2">
-        <v>298</v>
-      </c>
+      <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
         <v>75</v>
       </c>
@@ -6237,7 +6252,7 @@
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
@@ -6274,7 +6289,7 @@
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -6289,17 +6304,19 @@
         <v>233</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q43" s="2"/>
+      <c r="Q43" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="R43" t="s" s="2">
         <v>75</v>
       </c>
@@ -6343,19 +6360,19 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>236</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>75</v>
@@ -6364,7 +6381,7 @@
         <v>75</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -6372,21 +6389,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>75</v>
@@ -6398,17 +6415,15 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6457,28 +6472,28 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>75</v>
@@ -6486,14 +6501,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>243</v>
+        <v>146</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6506,26 +6521,24 @@
         <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O45" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
@@ -6573,7 +6586,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6594,7 +6607,7 @@
         <v>75</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>130</v>
+        <v>241</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>75</v>
@@ -6602,42 +6615,46 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>303</v>
+        <v>248</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
       </c>
@@ -6661,13 +6678,13 @@
         <v>75</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>305</v>
+        <v>75</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>75</v>
@@ -6685,19 +6702,19 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
@@ -6706,7 +6723,7 @@
         <v>75</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
@@ -6714,10 +6731,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6740,13 +6757,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6773,13 +6790,13 @@
         <v>75</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>75</v>
+        <v>310</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>75</v>
@@ -6797,7 +6814,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>87</v>
@@ -6837,10 +6854,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>75</v>
@@ -6849,27 +6866,23 @@
         <v>75</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>174</v>
+        <v>312</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N48" t="s" s="2">
         <v>314</v>
       </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q48" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
         <v>75</v>
       </c>
@@ -6889,13 +6902,13 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>316</v>
+        <v>75</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>317</v>
+        <v>75</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -6916,10 +6929,10 @@
         <v>311</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
@@ -6942,10 +6955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6968,22 +6981,24 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>320</v>
+        <v>174</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="R49" t="s" s="2">
         <v>75</v>
       </c>
@@ -7003,13 +7018,13 @@
         <v>75</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -7027,7 +7042,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7056,10 +7071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7082,16 +7097,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7117,13 +7132,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7141,7 +7156,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7170,10 +7185,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7196,16 +7211,16 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7231,11 +7246,13 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7253,7 +7270,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7282,10 +7299,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7308,16 +7325,16 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>174</v>
+        <v>324</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7347,7 +7364,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7365,7 +7382,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7394,10 +7411,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7408,7 +7425,7 @@
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>75</v>
@@ -7420,16 +7437,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>292</v>
+        <v>174</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7455,13 +7472,11 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>75</v>
+        <v>345</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7479,13 +7494,13 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>75</v>
@@ -7522,7 +7537,7 @@
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -7534,7 +7549,7 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>229</v>
+        <v>296</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>347</v>
@@ -7542,14 +7557,14 @@
       <c r="M54" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="N54" s="2"/>
+      <c r="N54" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q54" t="s" s="2">
-        <v>349</v>
-      </c>
+      <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
         <v>75</v>
       </c>
@@ -7599,7 +7614,7 @@
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>75</v>
@@ -7614,7 +7629,7 @@
         <v>75</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>192</v>
+        <v>75</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>75</v>
@@ -7636,7 +7651,7 @@
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>75</v>
@@ -7645,23 +7660,25 @@
         <v>75</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>233</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>234</v>
+        <v>351</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q55" s="2"/>
+      <c r="Q55" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="R55" t="s" s="2">
         <v>75</v>
       </c>
@@ -7705,19 +7722,19 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>236</v>
+        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -7726,7 +7743,7 @@
         <v>75</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>75</v>
@@ -7734,21 +7751,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -7760,17 +7777,15 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7819,28 +7834,28 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>75</v>
@@ -7848,14 +7863,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>243</v>
+        <v>146</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7868,26 +7883,24 @@
         <v>75</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O57" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>75</v>
       </c>
@@ -7935,7 +7948,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7956,7 +7969,7 @@
         <v>75</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>130</v>
+        <v>241</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>75</v>
@@ -7964,42 +7977,46 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>354</v>
+        <v>248</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>75</v>
       </c>
@@ -8023,13 +8040,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>356</v>
+        <v>75</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -8047,19 +8064,19 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>353</v>
+        <v>250</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
@@ -8068,7 +8085,7 @@
         <v>75</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>75</v>
@@ -8076,10 +8093,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8102,13 +8119,13 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8135,13 +8152,13 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>75</v>
+        <v>361</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8159,7 +8176,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -8199,10 +8216,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>75</v>
@@ -8211,16 +8228,16 @@
         <v>75</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>78</v>
+        <v>363</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8274,10 +8291,10 @@
         <v>362</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>75</v>
@@ -8295,6 +8312,118 @@
         <v>75</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>75</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
